--- a/01-dcf-valuation/Danone_DCF_Model.xlsx
+++ b/01-dcf-valuation/Danone_DCF_Model.xlsx
@@ -20,7 +20,7 @@
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Assumptions!$A$1:$G$43</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$E$30</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$F$27</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$N$25</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$N$33</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">DCF!$A$1:$G$30</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Financials!$A$1:$S$21</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Sensitivity!$A$1:$G$16</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="138">
   <si>
     <t xml:space="preserve">Danone (Euronext Paris : BN) - DCF à 2 étages</t>
   </si>
@@ -151,13 +151,25 @@
     <t xml:space="preserve">Danone (VE/EBITDA de marché, calculé)</t>
   </si>
   <si>
+    <t xml:space="preserve">Danone</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nestlé (FY2025)</t>
   </si>
   <si>
+    <t xml:space="preserve">Nestlé</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unilever (FY2025)</t>
   </si>
   <si>
+    <t xml:space="preserve">Unilever</t>
+  </si>
+  <si>
     <t xml:space="preserve">General Mills (FY2026, année fiscale mai)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Mills</t>
   </si>
   <si>
     <t xml:space="preserve">CONTRÔLES DU MODÈLE</t>
@@ -443,19 +455,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="0.00\x;\(0.00&quot;x)&quot;;\-"/>
     <numFmt numFmtId="169" formatCode="0.0\x;\(0.0&quot;x)&quot;;\-"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="#,##0.0;\(#,##0.0\);\-"/>
-    <numFmt numFmtId="172" formatCode="0.000"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0&quot; €&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.0\x"/>
+    <numFmt numFmtId="172" formatCode="0.00"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0;\(#,##0.0\);\-"/>
+    <numFmt numFmtId="174" formatCode="0.000"/>
+    <numFmt numFmtId="175" formatCode="#,##0.0&quot; €&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,6 +562,20 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -606,16 +634,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFDE7"/>
-        <bgColor rgb="FFF9F9F9"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -644,152 +681,180 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -802,7 +867,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF1E7B34"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFB00020"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -842,18 +919,18 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FFB00020"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF0F6B5C"/>
-      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFDE7"/>
-      <rgbColor rgb="FFF9F9F9"/>
+      <rgbColor rgb="FFE0E0E0"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -864,10 +941,10 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF1E7B34"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFE0E0E0"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -881,7 +958,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FF666666"/>
-      <rgbColor rgb="FF878787"/>
+      <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF2E7D32"/>
       <rgbColor rgb="FF003300"/>
@@ -943,19 +1020,102 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Valeur par action"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valeur par action</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:srgbClr val="4f81bd"/>
             </a:solidFill>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="f9f9f9"/>
-              </a:solidFill>
-              <a:round/>
+            <a:ln w="0">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1f3864"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="bfbfbf"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
           <c:dLbls>
+            <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="1"/>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -965,14 +1125,14 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
+            <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
@@ -1014,13 +1174,13 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:gapWidth val="150"/>
+        <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="89511108"/>
-        <c:axId val="49496175"/>
+        <c:axId val="29553469"/>
+        <c:axId val="64204745"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89511108"/>
+        <c:axId val="29553469"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1031,11 +1191,10 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
-            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -1052,7 +1211,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49496175"/>
+        <c:crossAx val="64204745"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1060,66 +1219,23 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49496175"/>
+        <c:axId val="64204745"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>€ / action</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="0"/>
+        <c:numFmt formatCode="#,##0&quot; €&quot;" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
+          <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
-            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -1136,7 +1252,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89511108"/>
+        <c:crossAx val="29553469"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1147,30 +1263,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -1189,6 +1281,400 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>VE/EBITDA : Danone vs. comparables</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"VE/EBITDA"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VE/EBITDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4f81bd"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1f3864"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="bfbfbf"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="bfbfbf"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="bfbfbf"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0\x" sourceLinked="1"/>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:numFmt formatCode="0.0\x" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:numFmt formatCode="0.0\x" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.0\x" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:numFmt formatCode="0.0\x" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$G$18:$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Danone</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Nestlé</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Unilever</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>General Mills</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$D$18:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0\x;\(0.0"x)";\-</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11.4293364377183</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="0"/>
+        <c:axId val="95085780"/>
+        <c:axId val="96383280"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="95085780"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="96383280"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="96383280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="18"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.0\x" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="95085780"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1416,11 +1902,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="73585821"/>
-        <c:axId val="65812202"/>
+        <c:axId val="60834885"/>
+        <c:axId val="44033788"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="73585821"/>
+        <c:axId val="60834885"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1451,7 +1937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65812202"/>
+        <c:crossAx val="44033788"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1459,7 +1945,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65812202"/>
+        <c:axId val="44033788"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1534,7 +2020,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73585821"/>
+        <c:crossAx val="60834885"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1593,13 +2079,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>183600</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>36000</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>99360</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>147240</xdr:rowOff>
+      <xdr:rowOff>76680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1607,12 +2093,42 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7707600" y="983880"/>
-        <a:ext cx="4316400" cy="2516040"/>
+        <a:off x="7707600" y="800280"/>
+        <a:ext cx="4751280" cy="2591280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>99360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="7707600" y="3086280"/>
+        <a:ext cx="4751280" cy="2591280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1632,18 +2148,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>253440</xdr:colOff>
+      <xdr:colOff>252720</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>133560</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8155440" y="800280"/>
-        <a:ext cx="5756760" cy="2876760"/>
+        <a:ext cx="5756040" cy="2876040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2001,6 +2517,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="8" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2027,90 +2546,109 @@
       <c r="B6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="n">
         <f aca="false">DCF!C21</f>
         <v>84.1212050621768</v>
       </c>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="C7" s="12"/>
+      <c r="D7" s="13" t="n">
         <f aca="false">DCF!C22</f>
         <v>59.5</v>
       </c>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="C8" s="12"/>
+      <c r="D8" s="14" t="n">
         <f aca="false">DCF!C23</f>
         <v>0.413801765750871</v>
       </c>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="C9" s="12"/>
+      <c r="D9" s="15" t="n">
         <f aca="false">DCF!C17</f>
         <v>65913.7659936647</v>
       </c>
+      <c r="E9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="C10" s="12"/>
+      <c r="D10" s="15" t="n">
         <f aca="false">DCF!C19</f>
         <v>57483.7659936647</v>
       </c>
+      <c r="E10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="C11" s="12"/>
+      <c r="D11" s="16" t="n">
         <f aca="false">Assumptions!C27</f>
         <v>0.069250733361853</v>
       </c>
+      <c r="E11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="C12" s="12"/>
+      <c r="D12" s="16" t="n">
         <f aca="false">Assumptions!C28</f>
         <v>0.02</v>
       </c>
+      <c r="E12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="C13" s="12"/>
+      <c r="D13" s="17" t="n">
         <f aca="false">DCF!C24</f>
         <v>15.3466277051606</v>
       </c>
+      <c r="E13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="C14" s="12"/>
+      <c r="D14" s="17" t="n">
         <f aca="false">DCF!C25</f>
         <v>11.4293364377183</v>
       </c>
-    </row>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="18" t="s">
         <v>36</v>
       </c>
       <c r="F17" s="10"/>
@@ -2120,38 +2658,58 @@
       <c r="B18" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="C18" s="12"/>
+      <c r="D18" s="19" t="n">
         <f aca="false">DCF!C25</f>
         <v>11.4293364377183</v>
       </c>
+      <c r="E18" s="12"/>
+      <c r="G18" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="21" t="n">
         <v>14.1</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="G19" s="20" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="21" t="n">
         <v>12.7</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="G20" s="20" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="18" t="n">
+        <v>43</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="21" t="n">
         <v>9.25</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="G21" s="20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -2160,15 +2718,23 @@
       <c r="G24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="19" t="str">
+      <c r="B25" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="23" t="str">
         <f aca="false">Checks!C25</f>
         <v>Tous les contrôles sont OK</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2196,7 +2762,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2206,7 +2772,7 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -2215,108 +2781,108 @@
       <c r="G5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="20" t="n">
+      <c r="B6" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="24" t="n">
         <v>27283</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="20" t="n">
+      <c r="B7" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="24" t="n">
         <v>2799</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="20" t="n">
+      <c r="B8" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="24" t="n">
         <v>3665</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="20" t="n">
+      <c r="B9" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="24" t="n">
         <v>4295</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="20" t="n">
+      <c r="B10" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="24" t="n">
         <v>8430</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="21" t="n">
+      <c r="B11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="25" t="n">
         <v>59.5</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="20" t="n">
+      <c r="B12" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="24" t="n">
         <v>40659</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="22" t="n">
+      <c r="B13" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>0.56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="23" t="n">
+      <c r="B14" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="27" t="n">
         <f aca="false">C12/C11</f>
         <v>683.344537815126</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -2325,119 +2891,119 @@
       <c r="G17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="24" t="n">
+      <c r="B18" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="28" t="n">
         <v>0.049</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="24" t="n">
+      <c r="B19" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="22" t="n">
+      <c r="B20" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="26" t="n">
         <v>0.56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="24" t="n">
+      <c r="B21" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="28" t="n">
         <v>0.0425</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="24" t="n">
+      <c r="B22" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="28" t="n">
         <v>0.25</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="25" t="n">
+      <c r="B23" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="29" t="n">
         <f aca="false">C18+C20*C19</f>
         <v>0.077</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="25" t="n">
+      <c r="B24" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="29" t="n">
         <f aca="false">C21*(1-C22)</f>
         <v>0.031875</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="25" t="n">
+      <c r="B25" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="29" t="n">
         <f aca="false">C12/(C12+C10)</f>
         <v>0.828271099431645</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="25" t="n">
+      <c r="B26" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="29" t="n">
         <f aca="false">C10/(C12+C10)</f>
         <v>0.171728900568355</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="13" t="n">
+      <c r="B27" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="30" t="n">
         <f aca="false">C25*C23+C26*C24</f>
         <v>0.069250733361853</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="24" t="n">
+      <c r="C28" s="28" t="n">
         <v>0.02</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -2467,7 +3033,7 @@
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -2476,83 +3042,83 @@
       <c r="G35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="19" t="s">
+      <c r="B36" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="C36" s="23" t="s">
         <v>86</v>
       </c>
+      <c r="D36" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="24" t="n">
+      <c r="B37" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="D37" s="24" t="n">
+      <c r="D37" s="28" t="n">
         <v>0.035</v>
       </c>
-      <c r="E37" s="24" t="n">
+      <c r="E37" s="28" t="n">
         <v>0.035</v>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="28" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="24" t="n">
+      <c r="B38" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="28" t="n">
         <v>0.103</v>
       </c>
-      <c r="D38" s="24" t="n">
+      <c r="D38" s="28" t="n">
         <v>0.105</v>
       </c>
-      <c r="E38" s="24" t="n">
+      <c r="E38" s="28" t="n">
         <v>0.107</v>
       </c>
-      <c r="F38" s="24" t="n">
+      <c r="F38" s="28" t="n">
         <v>0.11</v>
       </c>
-      <c r="G38" s="24" t="n">
+      <c r="G38" s="28" t="n">
         <v>0.112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2583,7 +3149,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2593,7 +3159,7 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -2602,79 +3168,79 @@
       <c r="G5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11"/>
-      <c r="C6" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>97</v>
+      <c r="B6" s="22"/>
+      <c r="C6" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="20" t="n">
+      <c r="B7" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="24" t="n">
         <v>27622</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="24" t="n">
         <v>27376</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="24" t="n">
         <v>27283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="20" t="n">
+      <c r="B8" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="24" t="n">
         <v>3351</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="24" t="n">
         <v>3514</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="24" t="n">
         <v>3665</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="20" t="n">
+      <c r="B9" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="24" t="n">
         <v>2998</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="24" t="n">
         <v>2021</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="24" t="n">
         <v>1825</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="25" t="n">
+      <c r="B10" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="29" t="n">
         <f aca="false">C8/C7</f>
         <v>0.121316342046195</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="29" t="n">
         <f aca="false">D8/D7</f>
         <v>0.128360607831677</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="29" t="n">
         <f aca="false">E8/E7</f>
         <v>0.134332734669941</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -2683,51 +3249,51 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11"/>
-      <c r="C14" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>97</v>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="20" t="n">
+      <c r="B15" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="24" t="n">
         <v>2600</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="24" t="n">
         <v>3004</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="24" t="n">
         <v>2799</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="25" t="n">
+      <c r="B16" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="29" t="n">
         <f aca="false">C15/C7</f>
         <v>0.0941278690898559</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="29" t="n">
         <f aca="false">D15/D7</f>
         <v>0.109731151373466</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="29" t="n">
         <f aca="false">E15/E7</f>
         <v>0.102591357255434</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -2777,7 +3343,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2786,151 +3352,151 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11"/>
-      <c r="C5" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="23" t="s">
         <v>86</v>
       </c>
+      <c r="D5" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="26" t="n">
+      <c r="B6" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="31" t="n">
         <f aca="false">Assumptions!$C$6*(1+Assumptions!C37)</f>
         <v>28101.49</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="31" t="n">
         <f aca="false">C6*(1+Assumptions!D37)</f>
         <v>29085.04215</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="31" t="n">
         <f aca="false">D6*(1+Assumptions!E37)</f>
         <v>30103.01862525</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">E6*(1+Assumptions!F37)</f>
         <v>31006.1091840075</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="31" t="n">
         <f aca="false">F6*(1+Assumptions!G37)</f>
         <v>31781.2619136077</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="27" t="n">
+      <c r="B7" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="32" t="n">
         <f aca="false">Assumptions!C38</f>
         <v>0.103</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="32" t="n">
         <f aca="false">Assumptions!D38</f>
         <v>0.105</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="32" t="n">
         <f aca="false">Assumptions!E38</f>
         <v>0.107</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="32" t="n">
         <f aca="false">Assumptions!F38</f>
         <v>0.11</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="32" t="n">
         <f aca="false">Assumptions!G38</f>
         <v>0.112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="26" t="n">
+      <c r="B8" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="31" t="n">
         <f aca="false">C6*C7</f>
         <v>2894.45347</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="31" t="n">
         <f aca="false">D6*D7</f>
         <v>3053.92942575</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="31" t="n">
         <f aca="false">E6*E7</f>
         <v>3221.02299290175</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="31" t="n">
         <f aca="false">F6*F7</f>
         <v>3410.67201024083</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="31" t="n">
         <f aca="false">G6*G7</f>
         <v>3559.50133432406</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="28" t="n">
+      <c r="B10" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="33" t="n">
         <f aca="false">1/(1+Assumptions!$C$27)^1</f>
         <v>0.935234336343057</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="33" t="n">
         <f aca="false">1/(1+Assumptions!$C$27)^2</f>
         <v>0.874663263875039</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="33" t="n">
         <f aca="false">1/(1+Assumptions!$C$27)^3</f>
         <v>0.818015117113825</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="33" t="n">
         <f aca="false">1/(1+Assumptions!$C$27)^4</f>
         <v>0.765035825172536</v>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="33" t="n">
         <f aca="false">1/(1+Assumptions!$C$27)^5</f>
         <v>0.7154877722339</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="26" t="n">
+      <c r="B11" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="31" t="n">
         <f aca="false">C8*C10</f>
         <v>2706.99227009131</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="31" t="n">
         <f aca="false">D8*D10</f>
         <v>2671.15987917052</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="31" t="n">
         <f aca="false">E8*E10</f>
         <v>2634.84550076485</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="31" t="n">
         <f aca="false">F8*F10</f>
         <v>2609.28627574746</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="31" t="n">
         <f aca="false">G8*G10</f>
         <v>2546.77967995912</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -2939,116 +3505,116 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="29" t="n">
+      <c r="B14" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="34" t="n">
         <f aca="false">SUM(C11:G11)</f>
         <v>13169.0636057333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="29" t="n">
+      <c r="B15" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="34" t="n">
         <f aca="false">G8*(1+Assumptions!$C$28)/(Assumptions!$C$27-Assumptions!$C$28)</f>
         <v>73718.5238306052</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="29" t="n">
+      <c r="B16" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="34" t="n">
         <f aca="false">C15*G10</f>
         <v>52744.7023879314</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="35" t="n">
         <f aca="false">C14+C16</f>
         <v>65913.7659936647</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="30" t="n">
+      <c r="B18" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="36" t="n">
         <f aca="false">Assumptions!C10</f>
         <v>8430</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="14" t="n">
+      <c r="B19" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="35" t="n">
         <f aca="false">C17-C18</f>
         <v>57483.7659936647</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" s="31" t="n">
+      <c r="B20" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="37" t="n">
         <f aca="false">Assumptions!C14</f>
         <v>683.344537815126</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="12" t="n">
+      <c r="B21" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="38" t="n">
         <f aca="false">C19/C20</f>
         <v>84.1212050621768</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="39" t="n">
         <f aca="false">Assumptions!C11</f>
         <v>59.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="25" t="n">
+      <c r="B23" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="29" t="n">
         <f aca="false">C21/C22-1</f>
         <v>0.413801765750871</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C24" s="40" t="n">
         <f aca="false">C17/Assumptions!C9</f>
         <v>15.3466277051606</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C25" s="40" t="n">
         <f aca="false">(Assumptions!C12+Assumptions!C10)/Assumptions!C9</f>
         <v>11.4293364377183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -3108,176 +3674,176 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="13" t="n">
+      <c r="B4" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="30" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="30" t="n">
         <v>0.0175</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="30" t="n">
         <v>0.02</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="30" t="n">
         <v>0.0225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="30" t="n">
         <v>0.055</v>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C5" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B5-C$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>108.855503428909</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B5-D$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>115.863410655474</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E5" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B5-E$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>123.872447485834</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B5-F$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>133.113643828557</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="30" t="n">
         <v>0.06</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B6-C$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>95.2363502572475</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B6-D$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>100.629773924124</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B6-E$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>106.69737554936</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B6-F$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>113.573990724627</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="30" t="n">
         <v>0.065</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B7-C$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>84.3435271321003</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B7-D$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>88.605664043973</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B7-E$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>93.3413717238315</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B7-F$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>98.6342214836734</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="30" t="n">
         <v>0.069</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="42" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B8-C$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>77.083274256357</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="42" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B8-D$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>80.669004644268</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="42" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B8-E$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>84.6206258880882</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="42" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B8-F$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>88.9971526419966</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="30" t="n">
         <v>0.07</v>
       </c>
-      <c r="C9" s="34" t="n">
+      <c r="C9" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B9-C$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>75.4334354179424</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B9-D$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>78.874020783809</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E9" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B9-E$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>82.6586646862623</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B9-F$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>86.8416921573949</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="30" t="n">
         <v>0.075</v>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B10-C$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>68.0103441292256</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D10" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B10-D$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>70.8367627742669</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E10" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B10-E$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>73.9201285688575</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B10-F$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>77.2971482486471</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="30" t="n">
         <v>0.08</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B11-C$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>61.7310561737698</v>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D11" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B11-D$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>64.0871959197157</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B11-E$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>66.6396806444904</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="41" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B11-F$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
         <v>69.4141205627237</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -3333,79 +3899,79 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>125</v>
+      <c r="B5" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="19" t="str">
+      <c r="B6" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="23" t="str">
         <f aca="false">IF(Assumptions!C28&lt;Assumptions!C27,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="19" t="str">
+      <c r="B7" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="23" t="str">
         <f aca="false">IF(ROUND(Assumptions!C25+Assumptions!C26,4)=1,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="19" t="str">
+      <c r="B8" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="23" t="str">
         <f aca="false">IF(MIN(Assumptions!C38:G38)&gt;0,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="19" t="str">
+      <c r="B9" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="23" t="str">
         <f aca="false">IF(ROUND(DCF!C14+DCF!C16-DCF!C17,1)=0,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="19" t="str">
+      <c r="B10" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="23" t="str">
         <f aca="false">IF(ABS(Assumptions!C14*Assumptions!C11/Assumptions!C12-1)&lt;0.01,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="19" t="str">
+      <c r="B11" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="23" t="str">
         <f aca="false">IF(DCF!C19&gt;0,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="19" t="str">
+      <c r="B25" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="23" t="str">
         <f aca="false">IF(COUNTIF(D6:D11,"OK")=6,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
         <v>Tous les contrôles sont OK</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -3428,10 +3994,10 @@
     <mergeCell ref="B28:E30"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D11">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>D6="OK"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>D6&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/01-dcf-valuation/Danone_DCF_Model.xlsx
+++ b/01-dcf-valuation/Danone_DCF_Model.xlsx
@@ -21,7 +21,7 @@
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$E$30</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$F$27</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$N$33</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">DCF!$A$1:$G$30</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">DCF!$A$1:$G$41</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Financials!$A$1:$S$21</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Sensitivity!$A$1:$G$16</definedName>
   </definedNames>
@@ -34,8 +34,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Méthode : bêta directement observé (levered) auprès d'un fournisseur de données de marché, et non reconstruit par débêtisation/rebêtisation à partir d'un échantillon de comparables (Nestlé, Unilever, General Mills). Le guide BIWS (Breaking Into Wall Street) admet cette approche simplifiée lorsque les données de structure financière des comparables (dette nette, capitalisation, taux d'IS par société) ne sont pas réunies à une maille fiable, ce qui est le cas ici. La valeur de 0,20 affichée par une autre source (stockanalysis.com) a été écartée car hors norme pour le secteur (bêta sectoriel actifs alimentation/boissons généralement proche de 0,4-0,6, cf. Vernimmen, Corporate Finance).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Convention mid-year : les flux de trésorerie sont supposés perçus en moyenne au milieu de chaque exercice (période n-0,5), plutôt qu'en toute fin d'année. C'est la convention standard en modélisation DCF (guide BIWS, Breaking Into Wall Street) ; elle relève légèrement la valeur actualisée par rapport à une convention fin d'année.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hypothèse : la marge d'EBITDA FY2025 (15,7 %) est maintenue constante jusqu'en 2030 pour ce recoupement, distincte des marges de FCF déjà projetées dans l'onglet Assumptions.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nestlé, Unilever, General Mills : multiples EV/EBITDA déjà retenus dans le Dashboard de ce classeur.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="145">
   <si>
     <t xml:space="preserve">Danone (Euronext Paris : BN) - DCF à 2 étages</t>
   </si>
@@ -376,7 +444,7 @@
     <t xml:space="preserve">Free cash-flow</t>
   </si>
   <si>
-    <t xml:space="preserve">Facteur d'actualisation</t>
+    <t xml:space="preserve">Facteur d'actualisation (convention mid-year)</t>
   </si>
   <si>
     <t xml:space="preserve">VA du free cash-flow</t>
@@ -409,7 +477,25 @@
     <t xml:space="preserve">Écart DCF vs marché (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : le DCF ressort nettement au-dessus du cours de marché (écart positif), avec un multiple VE/EBITDA implicite plus proche de celui des grands comparables mondiaux (Nestlé ~14x, Unilever ~13x, voir onglet Checks) que le multiple de marché actuel de Danone. Point de prudence : le taux sans risque utilisé (OAT France, ~4,9 %) est élevé par rapport à sa moyenne longue, ce qui tend plutôt à réduire la valeur implicite - l'écart constaté n'est donc pas un artefact d'un WACC trop bas.</t>
+    <t xml:space="preserve">Lecture : le DCF ressort nettement au-dessus du cours de marché (écart positif), avec un multiple VE/EBITDA implicite plus proche de celui des grands comparables mondiaux (Nestlé ~14x, Unilever ~13x, voir onglet Checks) que le multiple de marché actuel de Danone. Point de prudence : le taux sans risque utilisé (OAT France, ~4,9 %) est élevé par rapport à sa moyenne longue, ce qui tend plutôt à réduire la valeur implicite : l'écart constaté n'est donc pas un artefact d'un WACC trop bas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECOUPEMENT DE LA VALEUR TERMINALE (MULTIPLE DE SORTIE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marge d'EBITDA FY2025 (hypothèse de projection)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA implicite, année 5 (2030)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple de sortie implicite (VT / EBITDA an 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple médian des comparables (cf. Dashboard)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : ce recoupement applique la méthode des multiples de sortie en complément de la méthode Gordon growth (cf. guide BIWS, Key Rule #4) : on reconvertit la valeur terminale obtenue par Gordon growth en un multiple implicite VE/EBITDA à l'année 5, à comparer avec les comparables boursiers déjà retenus pour Danone (onglet Dashboard). La marge d'EBITDA à l'année 5 est une hypothèse de projection (maintien de la marge FY2025), distincte des marges de FCF déjà projetées dans l'onglet Assumptions.</t>
   </si>
   <si>
     <t xml:space="preserve">Sensibilité - valeur implicite par action (€)</t>
@@ -418,7 +504,7 @@
     <t xml:space="preserve">WACC \ g terminale</t>
   </si>
   <si>
-    <t xml:space="preserve">Formule : somme des FCF actualisés sur la trajectoire de l'onglet DCF + valeur terminale (Gordon growth) au couple (WACC, g), moins la dette nette, divisé par le nombre d'actions.</t>
+    <t xml:space="preserve">Formule : somme des FCF actualisés (convention mid-year) sur la trajectoire de l'onglet DCF + valeur terminale (Gordon growth) au couple (WACC, g), moins la dette nette, divisé par le nombre d'actions.</t>
   </si>
   <si>
     <t xml:space="preserve">Contrôle</t>
@@ -443,6 +529,9 @@
   </si>
   <si>
     <t xml:space="preserve">Valeur des fonds propres positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple de sortie implicite (VT) du même ordre de grandeur que les comparables</t>
   </si>
   <si>
     <t xml:space="preserve">Synthèse</t>
@@ -469,7 +558,7 @@
     <numFmt numFmtId="174" formatCode="0.000"/>
     <numFmt numFmtId="175" formatCode="#,##0.0&quot; €&quot;"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -596,6 +685,11 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -681,180 +775,184 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1165,7 +1263,7 @@
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>84.1212050621768</c:v>
+                  <c:v>87.4051816034026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>59.5</c:v>
@@ -1176,11 +1274,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="29553469"/>
-        <c:axId val="64204745"/>
+        <c:axId val="83222352"/>
+        <c:axId val="18931914"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29553469"/>
+        <c:axId val="83222352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1211,7 +1309,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64204745"/>
+        <c:crossAx val="18931914"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1219,7 +1317,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64204745"/>
+        <c:axId val="18931914"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -1252,7 +1350,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29553469"/>
+        <c:crossAx val="83222352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1570,11 +1668,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="95085780"/>
-        <c:axId val="96383280"/>
+        <c:axId val="98022747"/>
+        <c:axId val="23337067"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="95085780"/>
+        <c:axId val="98022747"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1605,7 +1703,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96383280"/>
+        <c:crossAx val="23337067"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1613,7 +1711,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96383280"/>
+        <c:axId val="23337067"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="18"/>
@@ -1646,7 +1744,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95085780"/>
+        <c:crossAx val="98022747"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1902,11 +2000,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60834885"/>
-        <c:axId val="44033788"/>
+        <c:axId val="95145529"/>
+        <c:axId val="77292036"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60834885"/>
+        <c:axId val="95145529"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,7 +2035,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44033788"/>
+        <c:crossAx val="77292036"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1945,7 +2043,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44033788"/>
+        <c:axId val="77292036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2020,7 +2118,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60834885"/>
+        <c:crossAx val="95145529"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2083,9 +2181,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>99360</xdr:colOff>
+      <xdr:colOff>96120</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>76680</xdr:rowOff>
+      <xdr:rowOff>73440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2094,7 +2192,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7707600" y="800280"/>
-        <a:ext cx="4751280" cy="2591280"/>
+        <a:ext cx="4748040" cy="2588040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2113,9 +2211,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>99360</xdr:colOff>
+      <xdr:colOff>96120</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>38880</xdr:rowOff>
+      <xdr:rowOff>35640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2124,7 +2222,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7707600" y="3086280"/>
-        <a:ext cx="4751280" cy="2591280"/>
+        <a:ext cx="4748040" cy="2588040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2148,9 +2246,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>252720</xdr:colOff>
+      <xdr:colOff>249480</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>132840</xdr:rowOff>
+      <xdr:rowOff>129600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2159,7 +2257,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8155440" y="800280"/>
-        <a:ext cx="5756040" cy="2876040"/>
+        <a:ext cx="5752800" cy="2872800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2549,7 +2647,7 @@
       <c r="C6" s="12"/>
       <c r="D6" s="13" t="n">
         <f aca="false">DCF!C21</f>
-        <v>84.1212050621768</v>
+        <v>87.4051816034026</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -2571,7 +2669,7 @@
       <c r="C8" s="12"/>
       <c r="D8" s="14" t="n">
         <f aca="false">DCF!C23</f>
-        <v>0.413801765750871</v>
+        <v>0.468994648796682</v>
       </c>
       <c r="E8" s="12"/>
     </row>
@@ -2582,7 +2680,7 @@
       <c r="C9" s="12"/>
       <c r="D9" s="15" t="n">
         <f aca="false">DCF!C17</f>
-        <v>65913.7659936647</v>
+        <v>68157.8534254243</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -2593,7 +2691,7 @@
       <c r="C10" s="12"/>
       <c r="D10" s="15" t="n">
         <f aca="false">DCF!C19</f>
-        <v>57483.7659936647</v>
+        <v>59727.8534254243</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -2626,7 +2724,7 @@
       <c r="C13" s="12"/>
       <c r="D13" s="17" t="n">
         <f aca="false">DCF!C24</f>
-        <v>15.3466277051606</v>
+        <v>15.8691160478287</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -3132,6 +3230,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3334,7 +3433,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G30"/>
+  <dimension ref="B2:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48"/>
@@ -3449,24 +3548,24 @@
         <v>113</v>
       </c>
       <c r="C10" s="33" t="n">
-        <f aca="false">1/(1+Assumptions!$C$27)^1</f>
-        <v>0.935234336343057</v>
+        <f aca="false">1/(1+Assumptions!$C$27)^0.5</f>
+        <v>0.967075145137676</v>
       </c>
       <c r="D10" s="33" t="n">
-        <f aca="false">1/(1+Assumptions!$C$27)^2</f>
-        <v>0.874663263875039</v>
+        <f aca="false">1/(1+Assumptions!$C$27)^1.5</f>
+        <v>0.9044418815567</v>
       </c>
       <c r="E10" s="33" t="n">
-        <f aca="false">1/(1+Assumptions!$C$27)^3</f>
-        <v>0.818015117113825</v>
+        <f aca="false">1/(1+Assumptions!$C$27)^2.5</f>
+        <v>0.845865102858547</v>
       </c>
       <c r="F10" s="33" t="n">
-        <f aca="false">1/(1+Assumptions!$C$27)^4</f>
-        <v>0.765035825172536</v>
+        <f aca="false">1/(1+Assumptions!$C$27)^3.5</f>
+        <v>0.791082088107665</v>
       </c>
       <c r="G10" s="33" t="n">
-        <f aca="false">1/(1+Assumptions!$C$27)^5</f>
-        <v>0.7154877722339</v>
+        <f aca="false">1/(1+Assumptions!$C$27)^4.5</f>
+        <v>0.739847131664252</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3475,23 +3574,23 @@
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">C8*C10</f>
-        <v>2706.99227009131</v>
+        <v>2799.1540095945</v>
       </c>
       <c r="D11" s="31" t="n">
         <f aca="false">D8*D10</f>
-        <v>2671.15987917052</v>
+        <v>2762.1016759667</v>
       </c>
       <c r="E11" s="31" t="n">
         <f aca="false">E8*E10</f>
-        <v>2634.84550076485</v>
+        <v>2724.55094520058</v>
       </c>
       <c r="F11" s="31" t="n">
         <f aca="false">F8*F10</f>
-        <v>2609.28627574746</v>
+        <v>2698.12153571168</v>
       </c>
       <c r="G11" s="31" t="n">
         <f aca="false">G8*G10</f>
-        <v>2546.77967995912</v>
+        <v>2633.48685235473</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3510,7 +3609,7 @@
       </c>
       <c r="C14" s="34" t="n">
         <f aca="false">SUM(C11:G11)</f>
-        <v>13169.0636057333</v>
+        <v>13617.4150188282</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3528,7 +3627,7 @@
       </c>
       <c r="C16" s="34" t="n">
         <f aca="false">C15*G10</f>
-        <v>52744.7023879314</v>
+        <v>54540.4384065961</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3537,7 +3636,7 @@
       </c>
       <c r="C17" s="35" t="n">
         <f aca="false">C14+C16</f>
-        <v>65913.7659936647</v>
+        <v>68157.8534254243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3555,7 +3654,7 @@
       </c>
       <c r="C19" s="35" t="n">
         <f aca="false">C17-C18</f>
-        <v>57483.7659936647</v>
+        <v>59727.8534254243</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3573,7 +3672,7 @@
       </c>
       <c r="C21" s="38" t="n">
         <f aca="false">C19/C20</f>
-        <v>84.1212050621768</v>
+        <v>87.4051816034026</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3591,7 +3690,7 @@
       </c>
       <c r="C23" s="29" t="n">
         <f aca="false">C21/C22-1</f>
-        <v>0.413801765750871</v>
+        <v>0.468994648796682</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3600,7 +3699,7 @@
       </c>
       <c r="C24" s="40" t="n">
         <f aca="false">C17/Assumptions!C9</f>
-        <v>15.3466277051606</v>
+        <v>15.8691160478287</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3646,9 +3745,90 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <f aca="false">Assumptions!C9/Assumptions!C6</f>
+        <v>0.157424036946084</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="34" t="n">
+        <f aca="false">G6*C33</f>
+        <v>5003.13454968094</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="41" t="n">
+        <f aca="false">C15/C34</f>
+        <v>14.7344675819895</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="40" t="n">
+        <f aca="false">MEDIAN(Dashboard!D19,Dashboard!D20,Dashboard!D21)</f>
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B27:G30"/>
+    <mergeCell ref="B38:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3657,6 +3837,10 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="30" man="true" max="16383" min="0"/>
+  </rowBreaks>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3674,12 +3858,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C4" s="30" t="n">
         <v>0.015</v>
@@ -3698,152 +3882,152 @@
       <c r="B5" s="30" t="n">
         <v>0.055</v>
       </c>
-      <c r="C5" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B5-C$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>108.855503428909</v>
-      </c>
-      <c r="D5" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B5-D$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>115.863410655474</v>
-      </c>
-      <c r="E5" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B5-E$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>123.872447485834</v>
-      </c>
-      <c r="F5" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B5-F$4)/(1+$B5)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>133.113643828557</v>
+      <c r="C5" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+C$4)/($B5-C$4)/(1+$B5)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>112.143673114572</v>
+      </c>
+      <c r="D5" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+D$4)/($B5-D$4)/(1+$B5)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>119.34171838391</v>
+      </c>
+      <c r="E5" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+E$4)/($B5-E$4)/(1+$B5)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>127.56805583458</v>
+      </c>
+      <c r="F5" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+F$4)/($B5-F$4)/(1+$B5)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>137.059983662278</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="30" t="n">
         <v>0.06</v>
       </c>
-      <c r="C6" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B6-C$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>95.2363502572475</v>
-      </c>
-      <c r="D6" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B6-D$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>100.629773924124</v>
-      </c>
-      <c r="E6" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B6-E$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>106.69737554936</v>
-      </c>
-      <c r="F6" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B6-F$4)/(1+$B6)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>113.573990724627</v>
+      <c r="C6" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+C$4)/($B6-C$4)/(1+$B6)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>98.4165244897869</v>
+      </c>
+      <c r="D6" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+D$4)/($B6-D$4)/(1+$B6)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>103.969394016567</v>
+      </c>
+      <c r="E6" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+E$4)/($B6-E$4)/(1+$B6)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>110.216372234196</v>
+      </c>
+      <c r="F6" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+F$4)/($B6-F$4)/(1+$B6)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>117.296280880841</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="30" t="n">
         <v>0.065</v>
       </c>
-      <c r="C7" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B7-C$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>84.3435271321003</v>
-      </c>
-      <c r="D7" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B7-D$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>88.605664043973</v>
-      </c>
-      <c r="E7" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B7-E$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>93.3413717238315</v>
-      </c>
-      <c r="F7" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B7-F$4)/(1+$B7)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>98.6342214836734</v>
+      <c r="C7" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+C$4)/($B7-C$4)/(1+$B7)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>87.4361600678272</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+D$4)/($B7-D$4)/(1+$B7)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>91.8346358008691</v>
+      </c>
+      <c r="E7" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+E$4)/($B7-E$4)/(1+$B7)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>96.7218310598045</v>
+      </c>
+      <c r="F7" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+F$4)/($B7-F$4)/(1+$B7)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>102.18399046685</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="30" t="n">
         <v>0.069</v>
       </c>
-      <c r="C8" s="42" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B8-C$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>77.083274256357</v>
-      </c>
-      <c r="D8" s="42" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B8-D$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>80.669004644268</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B8-E$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>84.6206258880882</v>
-      </c>
-      <c r="F8" s="42" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B8-F$4)/(1+$B8)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>88.9971526419966</v>
+      <c r="C8" s="43" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+C$4)/($B8-C$4)/(1+$B8)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>80.1167969700016</v>
+      </c>
+      <c r="D8" s="43" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+D$4)/($B8-D$4)/(1+$B8)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>83.8241716909339</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+E$4)/($B8-E$4)/(1+$B8)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>87.9098499548185</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+F$4)/($B8-F$4)/(1+$B8)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>92.4348484621316</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="30" t="n">
         <v>0.07</v>
       </c>
-      <c r="C9" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B9-C$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>75.4334354179424</v>
-      </c>
-      <c r="D9" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B9-D$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>78.874020783809</v>
-      </c>
-      <c r="E9" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B9-E$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>82.6586646862623</v>
-      </c>
-      <c r="F9" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B9-F$4)/(1+$B9)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>86.8416921573949</v>
+      <c r="C9" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+C$4)/($B9-C$4)/(1+$B9)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>78.4534231316937</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+D$4)/($B9-D$4)/(1+$B9)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>82.0123923077337</v>
+      </c>
+      <c r="E9" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+E$4)/($B9-E$4)/(1+$B9)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>85.9272584013777</v>
+      </c>
+      <c r="F9" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+F$4)/($B9-F$4)/(1+$B9)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>90.2542156627736</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="30" t="n">
         <v>0.075</v>
       </c>
-      <c r="C10" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B10-C$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>68.0103441292256</v>
-      </c>
-      <c r="D10" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B10-D$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>70.8367627742669</v>
-      </c>
-      <c r="E10" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B10-E$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>73.9201285688575</v>
-      </c>
-      <c r="F10" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B10-F$4)/(1+$B10)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>77.2971482486471</v>
+      <c r="C10" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+C$4)/($B10-C$4)/(1+$B10)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>70.9688767556136</v>
+      </c>
+      <c r="D10" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+D$4)/($B10-D$4)/(1+$B10)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>73.8993699792562</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+E$4)/($B10-E$4)/(1+$B10)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>77.0962716777753</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+F$4)/($B10-F$4)/(1+$B10)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>80.5976402047249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="30" t="n">
         <v>0.08</v>
       </c>
-      <c r="C11" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+C$4)/($B11-C$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>61.7310561737698</v>
-      </c>
-      <c r="D11" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+D$4)/($B11-D$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>64.0871959197157</v>
-      </c>
-      <c r="E11" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+E$4)/($B11-E$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>66.6396806444904</v>
-      </c>
-      <c r="F11" s="41" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$8*(1+F$4)/($B11-F$4)/(1+$B11)^5-Assumptions!$C$10)/Assumptions!$C$14</f>
-        <v>69.4141205627237</v>
+      <c r="C11" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+C$4)/($B11-C$4)/(1+$B11)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>64.6367577047684</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+D$4)/($B11-D$4)/(1+$B11)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>67.0853299545949</v>
+      </c>
+      <c r="E11" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+E$4)/($B11-E$4)/(1+$B11)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>69.7379498919068</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <f aca="false">(SUMPRODUCT(DCF!$C$8:$G$8,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$8*(1+F$4)/($B11-F$4)/(1+$B11)^4.5-Assumptions!$C$10)/Assumptions!$C$14</f>
+        <v>72.6212324324632</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -3900,15 +4084,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="43" t="s">
-        <v>130</v>
+      <c r="B6" s="44" t="s">
+        <v>136</v>
       </c>
       <c r="D6" s="23" t="str">
         <f aca="false">IF(Assumptions!C28&lt;Assumptions!C27,"OK","A VERIFIER")</f>
@@ -3916,8 +4100,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="43" t="s">
-        <v>131</v>
+      <c r="B7" s="44" t="s">
+        <v>137</v>
       </c>
       <c r="D7" s="23" t="str">
         <f aca="false">IF(ROUND(Assumptions!C25+Assumptions!C26,4)=1,"OK","A VERIFIER")</f>
@@ -3925,8 +4109,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="43" t="s">
-        <v>132</v>
+      <c r="B8" s="44" t="s">
+        <v>138</v>
       </c>
       <c r="D8" s="23" t="str">
         <f aca="false">IF(MIN(Assumptions!C38:G38)&gt;0,"OK","A VERIFIER")</f>
@@ -3934,8 +4118,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="43" t="s">
-        <v>133</v>
+      <c r="B9" s="44" t="s">
+        <v>139</v>
       </c>
       <c r="D9" s="23" t="str">
         <f aca="false">IF(ROUND(DCF!C14+DCF!C16-DCF!C17,1)=0,"OK","A VERIFIER")</f>
@@ -3943,8 +4127,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="43" t="s">
-        <v>134</v>
+      <c r="B10" s="44" t="s">
+        <v>140</v>
       </c>
       <c r="D10" s="23" t="str">
         <f aca="false">IF(ABS(Assumptions!C14*Assumptions!C11/Assumptions!C12-1)&lt;0.01,"OK","A VERIFIER")</f>
@@ -3952,26 +4136,35 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="43" t="s">
-        <v>135</v>
+      <c r="B11" s="44" t="s">
+        <v>141</v>
       </c>
       <c r="D11" s="23" t="str">
         <f aca="false">IF(DCF!C19&gt;0,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="23" t="str">
+        <f aca="false">IF(AND(DCF!C35&gt;=0.5*DCF!C36,DCF!C35&lt;=2*DCF!C36),"OK","A VERIFIER")</f>
+        <v>OK</v>
+      </c>
+    </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="23" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C25" s="23" t="str">
-        <f aca="false">IF(COUNTIF(D6:D11,"OK")=6,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
+        <f aca="false">IF(COUNTIF(D6:D13,"OK")=7,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
         <v>Tous les contrôles sont OK</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
